--- a/sp_aguas.xlsx
+++ b/sp_aguas.xlsx
@@ -653,8 +653,6 @@
           <t>CD4</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>2026-09-10</t>
@@ -675,7 +673,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>1</v>
       </c>

--- a/sp_aguas.xlsx
+++ b/sp_aguas.xlsx
@@ -13,8 +13,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'usuarios'!$A$1:$I$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'demandas'!$A$1:$O$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'historico'!$A$1:$F$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'demandas'!$A$1:$O$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'historico'!$A$1:$F$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -532,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
@@ -687,8 +687,114 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>13700013397/2026-00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>TCE-SP</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>13700013397/2026-00	ETC - Contrato 2024/22/0076/00/01/00 /  TC 001703.989.25-1 (Execução Contratual)</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Aguardando área</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2026-09-11 14:04:51</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2026-09-11 14:04:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>13700014832/2025-24</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>TCE-SP</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Requerimento nº 17/2026 - Balanço 2025</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Aguardando área</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2026-09-11 14:22:27</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2026-09-11 14:22:27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O2"/>
+  <autoFilter ref="A1:O4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -699,7 +805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -794,8 +900,60 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CRIACAO</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Demanda cadastrada.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-09-11 14:04:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>CRIACAO</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Demanda cadastrada.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-09-11 14:22:27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F3"/>
+  <autoFilter ref="A1:F5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/sp_aguas.xlsx
+++ b/sp_aguas.xlsx
@@ -13,8 +13,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'usuarios'!$A$1:$I$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'demandas'!$A$1:$O$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'historico'!$A$1:$F$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'demandas'!$A$1:$O$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'historico'!$A$1:$F$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -532,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -653,6 +653,8 @@
           <t>CD4</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>2026-09-10</t>
@@ -665,7 +667,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Em análise</t>
+          <t>Respondido</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -673,6 +675,7 @@
           <t>Normal</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>1</v>
       </c>
@@ -683,7 +686,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-09-10 18:00:22</t>
+          <t>2026-09-11 19:10:22</t>
         </is>
       </c>
     </row>
@@ -793,8 +796,65 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>13700003752/2025-43</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>TCE-SP</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ETC - Contrato 2025 / TC - 016645.989.26-0 (Termo Aditivo)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Aguardando área</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2026-09-11 18:38:58</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2026-09-11 18:38:58</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O4"/>
+  <autoFilter ref="A1:O5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -805,7 +865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -952,8 +1012,60 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CRIACAO</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Demanda cadastrada.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-09-11 18:38:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EDICAO</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Demanda alterada.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-09-11 19:10:22</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F5"/>
+  <autoFilter ref="A1:F7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/sp_aguas.xlsx
+++ b/sp_aguas.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="usuarios" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="demandas" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="historico" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="usuarios" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="demandas" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="historico" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'usuarios'!$A$1:$I$2</definedName>
@@ -532,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:V5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -628,6 +628,41 @@
           <t>atualizado_em</t>
         </is>
       </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>numero_etc</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>doe_data</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>doe_edicao</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>doe_secao</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>doe_palavra_chave</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>doe_publicacao</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>doe_url</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -653,8 +688,6 @@
           <t>CD4</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>2026-09-10</t>
@@ -675,7 +708,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>1</v>
       </c>
@@ -815,9 +847,6 @@
           <t>ETC - Contrato 2025 / TC - 016645.989.26-0 (Termo Aditivo)</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>2026-09-15</t>
@@ -838,7 +867,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>1</v>
       </c>
